--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ47"/>
+  <dimension ref="A1:AZ48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3953,27 +3953,27 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131765843</v>
+        <v>136759053</v>
       </c>
       <c r="B31" t="n">
-        <v>58624</v>
+        <v>58162</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103042</v>
+        <v>103023</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3983,14 +3983,14 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -4000,10 +4000,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>567553</v>
+        <v>567414</v>
       </c>
       <c r="R31" t="n">
-        <v>6509570</v>
+        <v>6509506</v>
       </c>
       <c r="S31" t="n">
         <v>50</v>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4061,13 +4061,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131765843</t>
+          <t>https://artportalen.se/Sighting/136759053</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131861151</v>
+        <v>131765843</v>
       </c>
       <c r="B32" t="n">
         <v>58624</v>
@@ -4095,7 +4095,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
@@ -4110,10 +4114,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>567468</v>
+        <v>567553</v>
       </c>
       <c r="R32" t="n">
-        <v>6509548</v>
+        <v>6509570</v>
       </c>
       <c r="S32" t="n">
         <v>50</v>
@@ -4140,12 +4144,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2026-03-22</t>
+          <t>2026-03-19</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4171,13 +4175,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131861151</t>
+          <t>https://artportalen.se/Sighting/131765843</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132863077</v>
+        <v>131861151</v>
       </c>
       <c r="B33" t="n">
         <v>58624</v>
@@ -4220,10 +4224,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>567541</v>
+        <v>567468</v>
       </c>
       <c r="R33" t="n">
-        <v>6509560</v>
+        <v>6509548</v>
       </c>
       <c r="S33" t="n">
         <v>50</v>
@@ -4250,12 +4254,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-03-22</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4281,33 +4285,33 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132863077</t>
+          <t>https://artportalen.se/Sighting/131861151</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132110067</v>
+        <v>132863077</v>
       </c>
       <c r="B34" t="n">
-        <v>58658</v>
+        <v>58624</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>103044</v>
+        <v>103042</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4330,10 +4334,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>567468</v>
+        <v>567541</v>
       </c>
       <c r="R34" t="n">
-        <v>6509548</v>
+        <v>6509560</v>
       </c>
       <c r="S34" t="n">
         <v>50</v>
@@ -4360,12 +4364,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4391,13 +4395,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132110067</t>
+          <t>https://artportalen.se/Sighting/132863077</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132110198</v>
+        <v>132110067</v>
       </c>
       <c r="B35" t="n">
         <v>58658</v>
@@ -4440,10 +4444,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>567553</v>
+        <v>567468</v>
       </c>
       <c r="R35" t="n">
-        <v>6509570</v>
+        <v>6509548</v>
       </c>
       <c r="S35" t="n">
         <v>50</v>
@@ -4470,12 +4474,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4501,13 +4505,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132110198</t>
+          <t>https://artportalen.se/Sighting/132110067</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132455861</v>
+        <v>132110198</v>
       </c>
       <c r="B36" t="n">
         <v>58658</v>
@@ -4546,17 +4550,17 @@
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>567548</v>
+        <v>567553</v>
       </c>
       <c r="R36" t="n">
-        <v>6509541</v>
+        <v>6509570</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4580,12 +4584,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4611,13 +4615,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132455861</t>
+          <t>https://artportalen.se/Sighting/132110198</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132863104</v>
+        <v>132455861</v>
       </c>
       <c r="B37" t="n">
         <v>58658</v>
@@ -4656,17 +4660,17 @@
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>567541</v>
+        <v>567548</v>
       </c>
       <c r="R37" t="n">
-        <v>6509560</v>
+        <v>6509541</v>
       </c>
       <c r="S37" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4690,12 +4694,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4721,13 +4725,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132863104</t>
+          <t>https://artportalen.se/Sighting/132455861</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>133034492</v>
+        <v>132863104</v>
       </c>
       <c r="B38" t="n">
         <v>58658</v>
@@ -4770,10 +4774,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>567414</v>
+        <v>567541</v>
       </c>
       <c r="R38" t="n">
-        <v>6509506</v>
+        <v>6509560</v>
       </c>
       <c r="S38" t="n">
         <v>50</v>
@@ -4800,12 +4804,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2026-05-02</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4831,13 +4835,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133034492</t>
+          <t>https://artportalen.se/Sighting/132863104</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>133036146</v>
+        <v>133034492</v>
       </c>
       <c r="B39" t="n">
         <v>58658</v>
@@ -4880,10 +4884,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>567542</v>
+        <v>567414</v>
       </c>
       <c r="R39" t="n">
-        <v>6509592</v>
+        <v>6509506</v>
       </c>
       <c r="S39" t="n">
         <v>50</v>
@@ -4910,12 +4914,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2026-05-02</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4941,16 +4945,16 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133036146</t>
+          <t>https://artportalen.se/Sighting/133034492</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128725191</v>
+        <v>133036146</v>
       </c>
       <c r="B40" t="n">
-        <v>56876</v>
+        <v>58658</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4958,58 +4962,45 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>208257</v>
+        <v>103044</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kopparödla</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Anguis fragilis</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>567548</v>
+        <v>567542</v>
       </c>
       <c r="R40" t="n">
-        <v>6509541</v>
+        <v>6509592</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5033,22 +5024,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>15:00</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-09-26</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>15:15</t>
+          <t>2026-04-30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5057,7 +5038,6 @@
       <c r="AE40" t="b">
         <v>0</v>
       </c>
-      <c r="AF40" t="inlineStr"/>
       <c r="AG40" t="b">
         <v>0</v>
       </c>
@@ -5075,16 +5055,16 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128725191</t>
+          <t>https://artportalen.se/Sighting/133036146</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>133696004</v>
+        <v>128725191</v>
       </c>
       <c r="B41" t="n">
-        <v>56896</v>
+        <v>56876</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5111,7 +5091,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J41" t="inlineStr"/>
@@ -5123,23 +5103,27 @@
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>vilande</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>567573</v>
+        <v>567548</v>
       </c>
       <c r="R41" t="n">
-        <v>6509528</v>
+        <v>6509541</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5163,12 +5147,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2025-09-26</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5195,13 +5189,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133696004</t>
+          <t>https://artportalen.se/Sighting/128725191</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134480243</v>
+        <v>133696004</v>
       </c>
       <c r="B42" t="n">
         <v>56896</v>
@@ -5231,7 +5225,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J42" t="inlineStr"/>
@@ -5243,20 +5237,20 @@
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>vilande</t>
         </is>
       </c>
       <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Skogen norr om Sjöberga, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>567507</v>
+        <v>567573</v>
       </c>
       <c r="R42" t="n">
-        <v>6509595</v>
+        <v>6509528</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5283,12 +5277,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5315,16 +5309,16 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134480243</t>
+          <t>https://artportalen.se/Sighting/133696004</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134210232</v>
+        <v>134480243</v>
       </c>
       <c r="B43" t="n">
-        <v>107943</v>
+        <v>56896</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5332,50 +5326,51 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>219933</v>
+        <v>208257</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kattfot</t>
+          <t>Kopparödla</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Antennaria dioica</t>
+          <t>Anguis fragilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Gaertn.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>adult</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Skogen norr om Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>567573</v>
+        <v>567507</v>
       </c>
       <c r="R43" t="n">
-        <v>6509528</v>
+        <v>6509595</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5402,12 +5397,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5434,43 +5429,43 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134210232</t>
+          <t>https://artportalen.se/Sighting/134480243</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123307520</v>
+        <v>134210232</v>
       </c>
       <c r="B44" t="n">
-        <v>99195</v>
+        <v>107943</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>219933</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kattfot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Antennaria dioica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Gaertn.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -5478,19 +5473,23 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sjöberga 1:2, Ög</t>
+          <t>Sjöberga, Ög</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>567527</v>
+        <v>567573</v>
       </c>
       <c r="R44" t="n">
-        <v>6509582</v>
+        <v>6509528</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5517,27 +5516,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-08-19</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Uppdaterad tidigare observation av lokalen från i mars i år: då noterade vi 21 st plantor/tuvor. Nu i augusti -25 är det minst 30 st.  Juni -26: mossan delvis skadad på lokalen ( i våras), noterar nu 10 friska plantor/tuvor och blomknoppar på väg.</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5564,13 +5548,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123307520</t>
+          <t>https://artportalen.se/Sighting/134210232</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127679939</v>
+        <v>123307520</v>
       </c>
       <c r="B45" t="n">
         <v>99195</v>
@@ -5600,7 +5584,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -5617,10 +5601,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>567571</v>
+        <v>567527</v>
       </c>
       <c r="R45" t="n">
-        <v>6509585</v>
+        <v>6509582</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5665,6 +5649,11 @@
           <t>11:30</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Uppdaterad tidigare observation av lokalen från i mars i år: då noterade vi 21 st plantor/tuvor. Nu i augusti -25 är det minst 30 st.  Juni -26: mossan delvis skadad på lokalen ( i våras), noterar nu 10 friska plantor/tuvor och blomknoppar på väg.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5689,16 +5678,16 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/127679939</t>
+          <t>https://artportalen.se/Sighting/123307520</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129866829</v>
+        <v>127679939</v>
       </c>
       <c r="B46" t="n">
-        <v>99118</v>
+        <v>99195</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5733,19 +5722,22 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>567588</v>
+        <v>567571</v>
       </c>
       <c r="R46" t="n">
-        <v>6509596</v>
+        <v>6509585</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5767,34 +5759,40 @@
           <t>Kvillinge</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>E-Nor-0880</t>
-        </is>
-      </c>
       <c r="Y46" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-08-19</t>
         </is>
       </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AD46" t="b">
         <v>0</v>
       </c>
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Karin Nyström</t>
+          <t>Anette Källman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
@@ -5802,65 +5800,66 @@
           <t>Anette Källman</t>
         </is>
       </c>
-      <c r="AY46" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
+      <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129866829</t>
+          <t>https://artportalen.se/Sighting/127679939</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135331676</v>
+        <v>129866829</v>
       </c>
       <c r="B47" t="n">
-        <v>107785</v>
+        <v>99118</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>224272</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Guldgul ängskovall</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Melampyrum pratense var. hians</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Druce</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sjöberga, Ög</t>
+          <t>Sjöberga 1:2, Ög</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>567573</v>
+        <v>567588</v>
       </c>
       <c r="R47" t="n">
-        <v>6509528</v>
+        <v>6509596</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5882,14 +5881,19 @@
           <t>Kvillinge</t>
         </is>
       </c>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>E-Nor-0880</t>
+        </is>
+      </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2025-08-19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5898,14 +5902,13 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Anette Källman</t>
+          <t>Karin Nyström</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
@@ -5913,8 +5916,119 @@
           <t>Anette Källman</t>
         </is>
       </c>
-      <c r="AY47" t="inlineStr"/>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
       <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129866829</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>135331676</v>
+      </c>
+      <c r="B48" t="n">
+        <v>107785</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>224272</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Guldgul ängskovall</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Melampyrum pratense var. hians</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Druce</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Sjöberga, Ög</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>567573</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6509528</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Norrköping</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Kvillinge</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Anette Källman</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135331676</t>
         </is>
@@ -5968,6 +6082,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -1814,7 +1814,7 @@
         <v>136274293</v>
       </c>
       <c r="B12" t="n">
-        <v>58003</v>
+        <v>58005</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>136759053</v>
       </c>
       <c r="B31" t="n">
-        <v>58162</v>
+        <v>58164</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -3956,7 +3956,7 @@
         <v>136759053</v>
       </c>
       <c r="B31" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -3956,7 +3956,7 @@
         <v>136759053</v>
       </c>
       <c r="B31" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -3988,11 +3988,7 @@
       </c>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>

--- a/artfynd/A 11077-2025 artfynd.xlsx
+++ b/artfynd/A 11077-2025 artfynd.xlsx
@@ -3956,7 +3956,7 @@
         <v>136759053</v>
       </c>
       <c r="B31" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
